--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run10/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run10/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.0678,0.8431,0.0151,0.1710</t>
-  </si>
-  <si>
-    <t>0.0070,0.0177,0.0020,0.9929</t>
-  </si>
-  <si>
-    <t>0.1416,0.3193,0.0119,0.6926</t>
-  </si>
-  <si>
-    <t>0.0282,0.0447,0.0093,0.9704</t>
-  </si>
-  <si>
-    <t>0.9764,0.0228,0.0026,0.0044</t>
-  </si>
-  <si>
-    <t>0.9358,0.0457,0.0030,0.0216</t>
-  </si>
-  <si>
-    <t>0.8864,0.1632,0.0069,0.0076</t>
-  </si>
-  <si>
-    <t>0.9756,0.0212,0.0018,0.0058</t>
-  </si>
-  <si>
-    <t>0.9528,0.0466,0.0039,0.0092</t>
-  </si>
-  <si>
-    <t>0.9586,0.0625,0.0025,0.0033</t>
-  </si>
-  <si>
-    <t>0.9424,0.0737,0.0042,0.0080</t>
-  </si>
-  <si>
-    <t>0.9724,0.0323,0.0030,0.0040</t>
-  </si>
-  <si>
-    <t>0.2316,0.6142,0.1449,0.0470</t>
-  </si>
-  <si>
-    <t>0.4209,0.0539,0.5788,0.0168</t>
-  </si>
-  <si>
-    <t>0.1126,0.2508,0.6287,0.0044</t>
-  </si>
-  <si>
-    <t>0.0843,0.5905,0.5604,0.0357</t>
-  </si>
-  <si>
-    <t>0.4279,0.5036,0.1150,0.0292</t>
-  </si>
-  <si>
-    <t>0.0035,0.9928,0.0052,0.0004</t>
-  </si>
-  <si>
-    <t>0.0068,0.9874,0.0081,0.0005</t>
-  </si>
-  <si>
-    <t>0.0358,0.9566,0.0132,0.0024</t>
-  </si>
-  <si>
-    <t>0.0055,0.9910,0.0047,0.0004</t>
-  </si>
-  <si>
-    <t>0.0037,0.9919,0.0079,0.0003</t>
-  </si>
-  <si>
-    <t>0.5917,0.0407,0.4301,0.0278</t>
-  </si>
-  <si>
-    <t>0.4129,0.1989,0.3678,0.0606</t>
-  </si>
-  <si>
-    <t>0.0808,0.0149,0.9077,0.0184</t>
-  </si>
-  <si>
-    <t>0.4491,0.0627,0.5272,0.0231</t>
-  </si>
-  <si>
-    <t>0.5568,0.0260,0.5323,0.0090</t>
-  </si>
-  <si>
-    <t>0.3893,0.0340,0.5970,0.0520</t>
-  </si>
-  <si>
-    <t>0.0371,0.0098,0.9148,0.0547</t>
-  </si>
-  <si>
-    <t>0.0248,0.9570,0.0225,0.0035</t>
-  </si>
-  <si>
-    <t>0.2804,0.5956,0.1647,0.0542</t>
-  </si>
-  <si>
-    <t>0.0302,0.0484,0.9589,0.0226</t>
-  </si>
-  <si>
-    <t>0.0078,0.9787,0.0366,0.0011</t>
-  </si>
-  <si>
-    <t>0.2738,0.6981,0.0698,0.0551</t>
-  </si>
-  <si>
-    <t>0.0981,0.7798,0.1811,0.0104</t>
-  </si>
-  <si>
-    <t>0.2712,0.7946,0.0138,0.0042</t>
-  </si>
-  <si>
-    <t>0.0074,0.9833,0.0178,0.0012</t>
-  </si>
-  <si>
-    <t>0.0337,0.8709,0.3869,0.0386</t>
-  </si>
-  <si>
-    <t>0.1971,0.0755,0.5426,0.2844</t>
-  </si>
-  <si>
-    <t>0.1201,0.5314,0.4524,0.0857</t>
-  </si>
-  <si>
-    <t>0.3041,0.0737,0.5579,0.1434</t>
-  </si>
-  <si>
-    <t>0.1131,0.4562,0.6296,0.0480</t>
-  </si>
-  <si>
-    <t>0.0077,0.9826,0.0131,0.0014</t>
-  </si>
-  <si>
-    <t>0.0628,0.1010,0.8698,0.0416</t>
-  </si>
-  <si>
-    <t>0.0744,0.2538,0.0271,0.8643</t>
-  </si>
-  <si>
-    <t>0.0010,0.9958,0.0050,0.0013</t>
-  </si>
-  <si>
-    <t>0.0074,0.9818,0.0150,0.0022</t>
-  </si>
-  <si>
-    <t>0.0013,0.9951,0.0086,0.0014</t>
-  </si>
-  <si>
-    <t>0.0553,0.1496,0.8668,0.0725</t>
-  </si>
-  <si>
-    <t>0.0501,0.4638,0.7706,0.0292</t>
-  </si>
-  <si>
-    <t>0.1986,0.0645,0.7806,0.0261</t>
-  </si>
-  <si>
-    <t>0.0986,0.0135,0.8932,0.0339</t>
-  </si>
-  <si>
-    <t>0.0322,0.0712,0.9513,0.0175</t>
-  </si>
-  <si>
-    <t>0.0626,0.1790,0.8514,0.0101</t>
-  </si>
-  <si>
-    <t>0.7699,0.3632,0.0043,0.0039</t>
-  </si>
-  <si>
-    <t>0.9186,0.0531,0.0146,0.0164</t>
-  </si>
-  <si>
-    <t>0.8252,0.2416,0.0097,0.0106</t>
-  </si>
-  <si>
-    <t>0.0233,0.0979,0.9617,0.0220</t>
-  </si>
-  <si>
-    <t>0.9142,0.0977,0.0041,0.0136</t>
-  </si>
-  <si>
-    <t>0.9589,0.0603,0.0022,0.0021</t>
-  </si>
-  <si>
-    <t>0.4446,0.6535,0.0098,0.0136</t>
-  </si>
-  <si>
-    <t>0.0060,0.9694,0.3616,0.0038</t>
-  </si>
-  <si>
-    <t>0.0619,0.2940,0.8870,0.0284</t>
-  </si>
-  <si>
-    <t>0.1435,0.1779,0.7530,0.0789</t>
-  </si>
-  <si>
-    <t>0.0120,0.8402,0.7727,0.0059</t>
-  </si>
-  <si>
-    <t>0.0136,0.0199,0.9736,0.0262</t>
-  </si>
-  <si>
-    <t>0.0094,0.9861,0.0053,0.0004</t>
-  </si>
-  <si>
-    <t>0.0056,0.9932,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.3604,0.2028,0.5020,0.0162</t>
-  </si>
-  <si>
-    <t>0.1629,0.7304,0.1068,0.0066</t>
-  </si>
-  <si>
-    <t>0.1021,0.5085,0.5363,0.0348</t>
-  </si>
-  <si>
-    <t>0.0055,0.9654,0.2798,0.0072</t>
-  </si>
-  <si>
-    <t>0.0047,0.9725,0.2530,0.0055</t>
-  </si>
-  <si>
-    <t>0.0118,0.9715,0.0464,0.0034</t>
-  </si>
-  <si>
-    <t>0.0062,0.9692,0.3326,0.0030</t>
-  </si>
-  <si>
-    <t>0.0137,0.0148,0.0335,0.9792</t>
-  </si>
-  <si>
-    <t>0.0030,0.0176,0.0018,0.9955</t>
-  </si>
-  <si>
-    <t>0.0050,0.0290,0.0012,0.9941</t>
-  </si>
-  <si>
-    <t>0.0038,0.0203,0.0023,0.9946</t>
-  </si>
-  <si>
-    <t>0.0036,0.0184,0.0030,0.9944</t>
-  </si>
-  <si>
-    <t>0.0146,0.0117,0.0069,0.9864</t>
-  </si>
-  <si>
-    <t>0.0054,0.9713,0.2348,0.0029</t>
-  </si>
-  <si>
-    <t>0.0168,0.8723,0.6498,0.0084</t>
-  </si>
-  <si>
-    <t>0.0273,0.8393,0.5607,0.0201</t>
-  </si>
-  <si>
-    <t>0.0230,0.8955,0.3644,0.0161</t>
-  </si>
-  <si>
-    <t>0.0067,0.9296,0.7297,0.0020</t>
-  </si>
-  <si>
-    <t>0.0063,0.9580,0.3448,0.0036</t>
-  </si>
-  <si>
-    <t>0.9192,0.0991,0.0039,0.0125</t>
-  </si>
-  <si>
-    <t>0.7846,0.2979,0.0083,0.0094</t>
-  </si>
-  <si>
-    <t>0.7817,0.3300,0.0072,0.0061</t>
-  </si>
-  <si>
-    <t>0.9027,0.1379,0.0063,0.0049</t>
-  </si>
-  <si>
-    <t>0.8512,0.2235,0.0052,0.0111</t>
-  </si>
-  <si>
-    <t>0.9500,0.0543,0.0033,0.0100</t>
-  </si>
-  <si>
-    <t>0.8502,0.2295,0.0055,0.0065</t>
-  </si>
-  <si>
-    <t>0.9348,0.0656,0.0062,0.0138</t>
-  </si>
-  <si>
-    <t>0.9705,0.0246,0.0016,0.0075</t>
-  </si>
-  <si>
-    <t>0.9595,0.0554,0.0027,0.0043</t>
-  </si>
-  <si>
-    <t>0.9663,0.0259,0.0025,0.0094</t>
-  </si>
-  <si>
-    <t>0.9802,0.0183,0.0017,0.0041</t>
-  </si>
-  <si>
-    <t>0.9488,0.0504,0.0035,0.0114</t>
-  </si>
-  <si>
-    <t>0.9497,0.0705,0.0041,0.0054</t>
-  </si>
-  <si>
-    <t>0.9281,0.0866,0.0049,0.0120</t>
-  </si>
-  <si>
-    <t>0.9498,0.0387,0.0039,0.0143</t>
-  </si>
-  <si>
-    <t>0.0519,0.0188,0.9511,0.0197</t>
-  </si>
-  <si>
-    <t>0.2861,0.1156,0.6232,0.0150</t>
-  </si>
-  <si>
-    <t>0.4501,0.2260,0.3244,0.0996</t>
-  </si>
-  <si>
-    <t>0.2883,0.0486,0.7180,0.0237</t>
-  </si>
-  <si>
-    <t>0.0181,0.9797,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.0111,0.9843,0.0031,0.0009</t>
-  </si>
-  <si>
-    <t>0.0447,0.9589,0.0049,0.0015</t>
-  </si>
-  <si>
-    <t>0.0453,0.9537,0.0103,0.0006</t>
-  </si>
-  <si>
-    <t>0.0060,0.9896,0.0049,0.0007</t>
-  </si>
-  <si>
-    <t>0.0080,0.9885,0.0024,0.0004</t>
-  </si>
-  <si>
-    <t>0.0634,0.9440,0.0038,0.0017</t>
-  </si>
-  <si>
-    <t>0.2294,0.5280,0.1769,0.2273</t>
-  </si>
-  <si>
-    <t>0.4084,0.0320,0.6060,0.0382</t>
-  </si>
-  <si>
-    <t>0.1634,0.7250,0.0636,0.1110</t>
-  </si>
-  <si>
-    <t>0.1990,0.5480,0.1448,0.2856</t>
-  </si>
-  <si>
-    <t>0.0575,0.2782,0.0335,0.8698</t>
-  </si>
-  <si>
-    <t>0.0006,0.9970,0.0037,0.0035</t>
-  </si>
-  <si>
-    <t>0.0006,0.9971,0.0053,0.0015</t>
-  </si>
-  <si>
-    <t>0.0062,0.9853,0.0084,0.0034</t>
-  </si>
-  <si>
-    <t>0.0009,0.9954,0.0361,0.0017</t>
-  </si>
-  <si>
-    <t>0.0109,0.9800,0.0207,0.0005</t>
-  </si>
-  <si>
-    <t>0.3977,0.7139,0.0199,0.0045</t>
-  </si>
-  <si>
-    <t>0.1811,0.8653,0.0101,0.0025</t>
-  </si>
-  <si>
-    <t>0.3838,0.6925,0.0101,0.0159</t>
-  </si>
-  <si>
-    <t>0.9011,0.1239,0.0073,0.0093</t>
-  </si>
-  <si>
-    <t>0.7891,0.2082,0.0443,0.0251</t>
-  </si>
-  <si>
-    <t>0.7858,0.2571,0.0216,0.0133</t>
-  </si>
-  <si>
-    <t>0.9495,0.0753,0.0021,0.0050</t>
-  </si>
-  <si>
-    <t>0.7504,0.3681,0.0088,0.0073</t>
-  </si>
-  <si>
-    <t>0.7996,0.2199,0.0077,0.0252</t>
-  </si>
-  <si>
-    <t>0.7784,0.2721,0.0125,0.0049</t>
-  </si>
-  <si>
-    <t>0.0199,0.7461,0.6303,0.0045</t>
-  </si>
-  <si>
-    <t>0.0696,0.6526,0.4050,0.0116</t>
-  </si>
-  <si>
-    <t>0.0692,0.1998,0.8702,0.0135</t>
-  </si>
-  <si>
-    <t>0.0259,0.8679,0.3201,0.0198</t>
-  </si>
-  <si>
-    <t>0.5122,0.3135,0.1165,0.0917</t>
-  </si>
-  <si>
-    <t>0.2594,0.2200,0.4942,0.0080</t>
-  </si>
-  <si>
-    <t>0.4014,0.0407,0.6378,0.0125</t>
-  </si>
-  <si>
-    <t>0.4121,0.4041,0.1313,0.0432</t>
-  </si>
-  <si>
-    <t>0.0215,0.0471,0.0030,0.9781</t>
-  </si>
-  <si>
-    <t>0.0008,0.0068,0.0019,0.9982</t>
-  </si>
-  <si>
-    <t>0.0039,0.0103,0.0043,0.9950</t>
-  </si>
-  <si>
-    <t>0.0014,0.0253,0.0009,0.9971</t>
-  </si>
-  <si>
-    <t>0.0111,0.8878,0.7194,0.0071</t>
-  </si>
-  <si>
-    <t>0.9253,0.0877,0.0040,0.0127</t>
-  </si>
-  <si>
-    <t>0.2500,0.8047,0.0103,0.0074</t>
-  </si>
-  <si>
-    <t>0.9081,0.0927,0.0044,0.0164</t>
-  </si>
-  <si>
-    <t>0.2672,0.7903,0.0135,0.0044</t>
-  </si>
-  <si>
-    <t>0.5192,0.4954,0.0343,0.0361</t>
-  </si>
-  <si>
-    <t>0.6002,0.1743,0.1959,0.0904</t>
-  </si>
-  <si>
-    <t>0.9310,0.0439,0.0043,0.0315</t>
-  </si>
-  <si>
-    <t>0.0064,0.0356,0.9511,0.0918</t>
-  </si>
-  <si>
-    <t>0.6404,0.1350,0.0203,0.1685</t>
-  </si>
-  <si>
-    <t>0.4170,0.5079,0.0282,0.1014</t>
-  </si>
-  <si>
-    <t>0.0356,0.9534,0.0106,0.0058</t>
-  </si>
-  <si>
-    <t>0.5922,0.4255,0.0355,0.0103</t>
-  </si>
-  <si>
-    <t>0.2748,0.7508,0.0427,0.0098</t>
-  </si>
-  <si>
-    <t>0.0754,0.8854,0.0211,0.0535</t>
-  </si>
-  <si>
-    <t>0.1099,0.8712,0.0331,0.0116</t>
-  </si>
-  <si>
-    <t>0.2175,0.8069,0.0228,0.0119</t>
-  </si>
-  <si>
-    <t>0.9607,0.0461,0.0042,0.0054</t>
-  </si>
-  <si>
-    <t>0.9554,0.0471,0.0034,0.0081</t>
-  </si>
-  <si>
-    <t>0.9407,0.0728,0.0043,0.0079</t>
-  </si>
-  <si>
-    <t>0.8716,0.1110,0.0060,0.0312</t>
-  </si>
-  <si>
-    <t>0.9405,0.0807,0.0027,0.0065</t>
-  </si>
-  <si>
-    <t>0.8160,0.1863,0.0039,0.0316</t>
-  </si>
-  <si>
-    <t>0.9158,0.0977,0.0049,0.0111</t>
-  </si>
-  <si>
-    <t>0.9359,0.0523,0.0056,0.0210</t>
-  </si>
-  <si>
-    <t>0.1189,0.8949,0.0092,0.0042</t>
-  </si>
-  <si>
-    <t>0.3100,0.7823,0.0096,0.0026</t>
-  </si>
-  <si>
-    <t>0.1092,0.9101,0.0103,0.0027</t>
-  </si>
-  <si>
-    <t>0.0613,0.1793,0.8618,0.0030</t>
-  </si>
-  <si>
-    <t>0.4428,0.6886,0.0056,0.0057</t>
-  </si>
-  <si>
-    <t>0.0958,0.8955,0.0072,0.0146</t>
-  </si>
-  <si>
-    <t>0.8290,0.2555,0.0050,0.0072</t>
-  </si>
-  <si>
-    <t>0.3014,0.7733,0.0071,0.0049</t>
-  </si>
-  <si>
-    <t>0.0063,0.0708,0.9886,0.0024</t>
-  </si>
-  <si>
-    <t>0.7124,0.3851,0.0088,0.0048</t>
-  </si>
-  <si>
-    <t>0.0211,0.0099,0.9776,0.0049</t>
-  </si>
-  <si>
-    <t>0.0548,0.5416,0.7326,0.0361</t>
-  </si>
-  <si>
-    <t>0.3053,0.1636,0.5213,0.0217</t>
-  </si>
-  <si>
-    <t>0.0293,0.7179,0.7496,0.0234</t>
-  </si>
-  <si>
-    <t>0.2625,0.0475,0.7731,0.0158</t>
-  </si>
-  <si>
-    <t>0.0174,0.0148,0.9630,0.0381</t>
-  </si>
-  <si>
-    <t>0.0772,0.0387,0.9286,0.0070</t>
-  </si>
-  <si>
-    <t>0.2874,0.4600,0.2426,0.0314</t>
-  </si>
-  <si>
-    <t>0.3315,0.3226,0.3657,0.0467</t>
-  </si>
-  <si>
-    <t>0.4249,0.3358,0.1576,0.0208</t>
-  </si>
-  <si>
-    <t>0.0591,0.8778,0.0629,0.0291</t>
-  </si>
-  <si>
-    <t>0.2294,0.3620,0.3456,0.0075</t>
-  </si>
-  <si>
-    <t>0.2864,0.6607,0.0657,0.0255</t>
-  </si>
-  <si>
-    <t>0.3455,0.4826,0.1456,0.1318</t>
-  </si>
-  <si>
-    <t>0.2521,0.3808,0.2879,0.0074</t>
-  </si>
-  <si>
-    <t>0.2708,0.8048,0.0087,0.0045</t>
-  </si>
-  <si>
-    <t>0.1141,0.9101,0.0059,0.0017</t>
-  </si>
-  <si>
-    <t>0.1911,0.8533,0.0143,0.0049</t>
-  </si>
-  <si>
-    <t>0.8089,0.2944,0.0045,0.0058</t>
-  </si>
-  <si>
-    <t>0.3444,0.7826,0.0045,0.0033</t>
-  </si>
-  <si>
-    <t>0.5989,0.1342,0.1740,0.0290</t>
-  </si>
-  <si>
-    <t>0.6609,0.0526,0.3185,0.0227</t>
-  </si>
-  <si>
-    <t>0.1760,0.1816,0.0408,0.7366</t>
-  </si>
-  <si>
-    <t>0.3937,0.2686,0.3654,0.0844</t>
-  </si>
-  <si>
-    <t>0.5557,0.0771,0.2992,0.1116</t>
-  </si>
-  <si>
-    <t>0.0665,0.0711,0.8079,0.1808</t>
-  </si>
-  <si>
-    <t>0.0771,0.6026,0.4871,0.0596</t>
-  </si>
-  <si>
-    <t>0.1680,0.1574,0.7366,0.0306</t>
-  </si>
-  <si>
-    <t>0.1592,0.4863,0.4352,0.0555</t>
-  </si>
-  <si>
-    <t>0.1106,0.4857,0.5552,0.0649</t>
-  </si>
-  <si>
-    <t>0.9354,0.0768,0.0046,0.0102</t>
-  </si>
-  <si>
-    <t>0.9349,0.0816,0.0064,0.0060</t>
-  </si>
-  <si>
-    <t>0.9378,0.1105,0.0026,0.0030</t>
-  </si>
-  <si>
-    <t>0.8782,0.1978,0.0047,0.0065</t>
-  </si>
-  <si>
-    <t>0.9177,0.1160,0.0058,0.0047</t>
-  </si>
-  <si>
-    <t>0.9534,0.0735,0.0031,0.0028</t>
-  </si>
-  <si>
-    <t>0.9277,0.1011,0.0037,0.0085</t>
-  </si>
-  <si>
-    <t>0.9294,0.0952,0.0041,0.0073</t>
-  </si>
-  <si>
-    <t>0.0764,0.1850,0.8754,0.0171</t>
-  </si>
-  <si>
-    <t>0.5570,0.1780,0.2567,0.0149</t>
-  </si>
-  <si>
-    <t>0.3443,0.4222,0.0249,0.2360</t>
-  </si>
-  <si>
-    <t>0.0377,0.0171,0.9500,0.0175</t>
-  </si>
-  <si>
-    <t>0.0606,0.0347,0.8895,0.0530</t>
-  </si>
-  <si>
-    <t>0.0443,0.0373,0.9412,0.0035</t>
-  </si>
-  <si>
-    <t>0.0101,0.0152,0.9515,0.0911</t>
-  </si>
-  <si>
-    <t>0.2139,0.1236,0.6761,0.0598</t>
-  </si>
-  <si>
-    <t>0.0155,0.0098,0.9693,0.0255</t>
-  </si>
-  <si>
-    <t>0.1223,0.0494,0.6943,0.2417</t>
-  </si>
-  <si>
-    <t>0.1989,0.2948,0.4685,0.0118</t>
-  </si>
-  <si>
-    <t>0.5310,0.1788,0.2504,0.0899</t>
-  </si>
-  <si>
-    <t>0.5768,0.0267,0.3187,0.0919</t>
-  </si>
-  <si>
-    <t>0.5587,0.0933,0.3292,0.1138</t>
-  </si>
-  <si>
-    <t>0.9090,0.1373,0.0054,0.0061</t>
-  </si>
-  <si>
-    <t>0.9372,0.0938,0.0038,0.0027</t>
-  </si>
-  <si>
-    <t>0.9549,0.0646,0.0041,0.0023</t>
-  </si>
-  <si>
-    <t>0.8949,0.1696,0.0037,0.0059</t>
-  </si>
-  <si>
-    <t>0.9153,0.1317,0.0033,0.0074</t>
-  </si>
-  <si>
-    <t>0.8293,0.2520,0.0056,0.0083</t>
-  </si>
-  <si>
-    <t>0.8622,0.2275,0.0052,0.0039</t>
-  </si>
-  <si>
-    <t>0.8804,0.1779,0.0043,0.0091</t>
-  </si>
-  <si>
-    <t>0.0974,0.5058,0.4634,0.0176</t>
-  </si>
-  <si>
-    <t>0.0241,0.2134,0.9456,0.0060</t>
-  </si>
-  <si>
-    <t>0.0400,0.5432,0.7890,0.0213</t>
-  </si>
-  <si>
-    <t>0.2732,0.1647,0.5876,0.0449</t>
-  </si>
-  <si>
-    <t>0.0606,0.0185,0.9209,0.0327</t>
-  </si>
-  <si>
-    <t>0.3068,0.0408,0.6943,0.0415</t>
-  </si>
-  <si>
-    <t>0.2669,0.4432,0.3207,0.0995</t>
-  </si>
-  <si>
-    <t>0.1730,0.0389,0.7615,0.0688</t>
-  </si>
-  <si>
-    <t>0.4109,0.0591,0.0280,0.5808</t>
-  </si>
-  <si>
-    <t>0.0044,0.0692,0.0069,0.9876</t>
-  </si>
-  <si>
-    <t>0.0125,0.0274,0.0050,0.9873</t>
-  </si>
-  <si>
-    <t>0.0009,0.0085,0.0008,0.9986</t>
-  </si>
-  <si>
-    <t>0.0013,0.0096,0.0010,0.9981</t>
-  </si>
-  <si>
-    <t>0.0911,0.7154,0.0434,0.3792</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.2553,0.6497,0.0090,0.0926</t>
+  </si>
+  <si>
+    <t>0.0094,0.0347,0.0053,0.9876</t>
+  </si>
+  <si>
+    <t>0.4857,0.3120,0.0163,0.1894</t>
+  </si>
+  <si>
+    <t>0.0423,0.0565,0.0144,0.9566</t>
+  </si>
+  <si>
+    <t>0.9783,0.0255,0.0018,0.0031</t>
+  </si>
+  <si>
+    <t>0.9566,0.0449,0.0025,0.0095</t>
+  </si>
+  <si>
+    <t>0.9327,0.0984,0.0055,0.0041</t>
+  </si>
+  <si>
+    <t>0.9712,0.0202,0.0013,0.0093</t>
+  </si>
+  <si>
+    <t>0.9759,0.0260,0.0020,0.0044</t>
+  </si>
+  <si>
+    <t>0.9544,0.0754,0.0026,0.0019</t>
+  </si>
+  <si>
+    <t>0.9657,0.0394,0.0020,0.0067</t>
+  </si>
+  <si>
+    <t>0.9723,0.0208,0.0023,0.0101</t>
+  </si>
+  <si>
+    <t>0.1145,0.8220,0.0852,0.0204</t>
+  </si>
+  <si>
+    <t>0.3046,0.1372,0.4753,0.0070</t>
+  </si>
+  <si>
+    <t>0.5067,0.0301,0.5608,0.0055</t>
+  </si>
+  <si>
+    <t>0.0727,0.6268,0.4890,0.0404</t>
+  </si>
+  <si>
+    <t>0.1886,0.6626,0.1571,0.0266</t>
+  </si>
+  <si>
+    <t>0.0026,0.9942,0.0066,0.0004</t>
+  </si>
+  <si>
+    <t>0.0033,0.9921,0.0092,0.0003</t>
+  </si>
+  <si>
+    <t>0.0923,0.9162,0.0088,0.0028</t>
+  </si>
+  <si>
+    <t>0.0042,0.9924,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.0018,0.9957,0.0047,0.0002</t>
+  </si>
+  <si>
+    <t>0.5204,0.0402,0.4784,0.0243</t>
+  </si>
+  <si>
+    <t>0.4581,0.0596,0.3395,0.2100</t>
+  </si>
+  <si>
+    <t>0.1301,0.0164,0.8748,0.0140</t>
+  </si>
+  <si>
+    <t>0.3186,0.1702,0.5083,0.0315</t>
+  </si>
+  <si>
+    <t>0.2083,0.0506,0.7954,0.0078</t>
+  </si>
+  <si>
+    <t>0.3010,0.0201,0.6967,0.0387</t>
+  </si>
+  <si>
+    <t>0.0756,0.0151,0.8930,0.0394</t>
+  </si>
+  <si>
+    <t>0.1047,0.8968,0.0114,0.0029</t>
+  </si>
+  <si>
+    <t>0.1688,0.7890,0.0672,0.0352</t>
+  </si>
+  <si>
+    <t>0.0265,0.0961,0.9590,0.0129</t>
+  </si>
+  <si>
+    <t>0.0042,0.9888,0.0185,0.0003</t>
+  </si>
+  <si>
+    <t>0.5527,0.4083,0.0763,0.0308</t>
+  </si>
+  <si>
+    <t>0.3176,0.5958,0.0809,0.0121</t>
+  </si>
+  <si>
+    <t>0.4966,0.6422,0.0070,0.0048</t>
+  </si>
+  <si>
+    <t>0.0103,0.9784,0.0239,0.0032</t>
+  </si>
+  <si>
+    <t>0.0583,0.8105,0.3376,0.0358</t>
+  </si>
+  <si>
+    <t>0.1187,0.4969,0.5944,0.0633</t>
+  </si>
+  <si>
+    <t>0.0692,0.6105,0.4968,0.0163</t>
+  </si>
+  <si>
+    <t>0.2993,0.0158,0.7468,0.0212</t>
+  </si>
+  <si>
+    <t>0.0807,0.3848,0.7619,0.0483</t>
+  </si>
+  <si>
+    <t>0.0146,0.9647,0.0221,0.0051</t>
+  </si>
+  <si>
+    <t>0.1136,0.0400,0.8445,0.0641</t>
+  </si>
+  <si>
+    <t>0.0062,0.9142,0.0103,0.5035</t>
+  </si>
+  <si>
+    <t>0.0012,0.9954,0.0038,0.0015</t>
+  </si>
+  <si>
+    <t>0.0015,0.9946,0.0079,0.0015</t>
+  </si>
+  <si>
+    <t>0.0005,0.9975,0.0079,0.0011</t>
+  </si>
+  <si>
+    <t>0.0544,0.2499,0.8733,0.0268</t>
+  </si>
+  <si>
+    <t>0.0445,0.2799,0.8819,0.0309</t>
+  </si>
+  <si>
+    <t>0.1854,0.0399,0.8495,0.0126</t>
+  </si>
+  <si>
+    <t>0.0779,0.0234,0.8900,0.0470</t>
+  </si>
+  <si>
+    <t>0.0223,0.0428,0.9685,0.0172</t>
+  </si>
+  <si>
+    <t>0.1223,0.1329,0.7618,0.0372</t>
+  </si>
+  <si>
+    <t>0.7339,0.4060,0.0042,0.0039</t>
+  </si>
+  <si>
+    <t>0.8779,0.1579,0.0097,0.0080</t>
+  </si>
+  <si>
+    <t>0.9166,0.1146,0.0078,0.0080</t>
+  </si>
+  <si>
+    <t>0.0866,0.0582,0.8263,0.1377</t>
+  </si>
+  <si>
+    <t>0.8877,0.1449,0.0051,0.0166</t>
+  </si>
+  <si>
+    <t>0.9249,0.1130,0.0037,0.0031</t>
+  </si>
+  <si>
+    <t>0.4565,0.6686,0.0076,0.0053</t>
+  </si>
+  <si>
+    <t>0.0184,0.9346,0.2922,0.0085</t>
+  </si>
+  <si>
+    <t>0.0584,0.0822,0.8934,0.0606</t>
+  </si>
+  <si>
+    <t>0.0764,0.4221,0.6651,0.0523</t>
+  </si>
+  <si>
+    <t>0.0051,0.9129,0.7800,0.0019</t>
+  </si>
+  <si>
+    <t>0.0095,0.0567,0.9775,0.0154</t>
+  </si>
+  <si>
+    <t>0.0092,0.9826,0.0129,0.0009</t>
+  </si>
+  <si>
+    <t>0.0013,0.9974,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.3237,0.2938,0.4206,0.0097</t>
+  </si>
+  <si>
+    <t>0.0989,0.8536,0.0940,0.0110</t>
+  </si>
+  <si>
+    <t>0.0112,0.0742,0.9810,0.0054</t>
+  </si>
+  <si>
+    <t>0.0065,0.9485,0.4532,0.0027</t>
+  </si>
+  <si>
+    <t>0.0051,0.9750,0.2124,0.0042</t>
+  </si>
+  <si>
+    <t>0.0078,0.9793,0.0277,0.0029</t>
+  </si>
+  <si>
+    <t>0.0052,0.9724,0.4308,0.0023</t>
+  </si>
+  <si>
+    <t>0.0056,0.0139,0.0026,0.9939</t>
+  </si>
+  <si>
+    <t>0.0013,0.0150,0.0012,0.9976</t>
+  </si>
+  <si>
+    <t>0.0078,0.0068,0.0031,0.9937</t>
+  </si>
+  <si>
+    <t>0.0036,0.0146,0.0013,0.9958</t>
+  </si>
+  <si>
+    <t>0.0133,0.0399,0.0193,0.9790</t>
+  </si>
+  <si>
+    <t>0.0127,0.0336,0.0081,0.9849</t>
+  </si>
+  <si>
+    <t>0.0077,0.9651,0.2083,0.0038</t>
+  </si>
+  <si>
+    <t>0.0270,0.8767,0.5384,0.0223</t>
+  </si>
+  <si>
+    <t>0.0243,0.8091,0.6596,0.0104</t>
+  </si>
+  <si>
+    <t>0.0319,0.6958,0.6583,0.0102</t>
+  </si>
+  <si>
+    <t>0.0144,0.9155,0.5300,0.0051</t>
+  </si>
+  <si>
+    <t>0.0042,0.9599,0.5090,0.0038</t>
+  </si>
+  <si>
+    <t>0.8768,0.1883,0.0049,0.0063</t>
+  </si>
+  <si>
+    <t>0.9214,0.1377,0.0031,0.0025</t>
+  </si>
+  <si>
+    <t>0.7612,0.3489,0.0074,0.0074</t>
+  </si>
+  <si>
+    <t>0.9408,0.0772,0.0048,0.0059</t>
+  </si>
+  <si>
+    <t>0.8892,0.1812,0.0032,0.0049</t>
+  </si>
+  <si>
+    <t>0.9734,0.0307,0.0016,0.0047</t>
+  </si>
+  <si>
+    <t>0.9346,0.0913,0.0050,0.0042</t>
+  </si>
+  <si>
+    <t>0.8776,0.1609,0.0094,0.0101</t>
+  </si>
+  <si>
+    <t>0.9410,0.0564,0.0028,0.0144</t>
+  </si>
+  <si>
+    <t>0.9470,0.0820,0.0030,0.0029</t>
+  </si>
+  <si>
+    <t>0.9717,0.0207,0.0014,0.0103</t>
+  </si>
+  <si>
+    <t>0.9674,0.0354,0.0026,0.0074</t>
+  </si>
+  <si>
+    <t>0.9152,0.1293,0.0066,0.0076</t>
+  </si>
+  <si>
+    <t>0.9772,0.0290,0.0022,0.0025</t>
+  </si>
+  <si>
+    <t>0.9559,0.0509,0.0035,0.0078</t>
+  </si>
+  <si>
+    <t>0.9695,0.0216,0.0027,0.0117</t>
+  </si>
+  <si>
+    <t>0.0595,0.0197,0.9116,0.0703</t>
+  </si>
+  <si>
+    <t>0.1033,0.0861,0.8668,0.0110</t>
+  </si>
+  <si>
+    <t>0.5448,0.0899,0.2838,0.1369</t>
+  </si>
+  <si>
+    <t>0.2721,0.0303,0.7445,0.0260</t>
+  </si>
+  <si>
+    <t>0.0160,0.9786,0.0041,0.0012</t>
+  </si>
+  <si>
+    <t>0.0205,0.9776,0.0033,0.0005</t>
+  </si>
+  <si>
+    <t>0.0961,0.9287,0.0032,0.0008</t>
+  </si>
+  <si>
+    <t>0.0523,0.9500,0.0066,0.0009</t>
+  </si>
+  <si>
+    <t>0.0085,0.9865,0.0055,0.0009</t>
+  </si>
+  <si>
+    <t>0.0071,0.9887,0.0035,0.0007</t>
+  </si>
+  <si>
+    <t>0.1417,0.8935,0.0039,0.0023</t>
+  </si>
+  <si>
+    <t>0.3258,0.4644,0.1471,0.1255</t>
+  </si>
+  <si>
+    <t>0.1593,0.1124,0.7805,0.0100</t>
+  </si>
+  <si>
+    <t>0.1174,0.6185,0.0775,0.3434</t>
+  </si>
+  <si>
+    <t>0.1978,0.6742,0.1208,0.1009</t>
+  </si>
+  <si>
+    <t>0.0418,0.4871,0.0343,0.8134</t>
+  </si>
+  <si>
+    <t>0.0008,0.9964,0.0073,0.0015</t>
+  </si>
+  <si>
+    <t>0.0011,0.9954,0.0057,0.0017</t>
+  </si>
+  <si>
+    <t>0.0028,0.9880,0.0066,0.0089</t>
+  </si>
+  <si>
+    <t>0.0007,0.9959,0.0420,0.0015</t>
+  </si>
+  <si>
+    <t>0.0198,0.9678,0.0228,0.0012</t>
+  </si>
+  <si>
+    <t>0.2974,0.7721,0.0129,0.0034</t>
+  </si>
+  <si>
+    <t>0.4812,0.6292,0.0125,0.0026</t>
+  </si>
+  <si>
+    <t>0.7159,0.3699,0.0072,0.0101</t>
+  </si>
+  <si>
+    <t>0.8907,0.0547,0.0033,0.0524</t>
+  </si>
+  <si>
+    <t>0.8664,0.1341,0.0153,0.0288</t>
+  </si>
+  <si>
+    <t>0.8180,0.2286,0.0047,0.0149</t>
+  </si>
+  <si>
+    <t>0.8817,0.0614,0.0049,0.0588</t>
+  </si>
+  <si>
+    <t>0.9017,0.1148,0.0080,0.0068</t>
+  </si>
+  <si>
+    <t>0.5443,0.4751,0.0111,0.0389</t>
+  </si>
+  <si>
+    <t>0.8746,0.1898,0.0057,0.0037</t>
+  </si>
+  <si>
+    <t>0.0082,0.8805,0.7118,0.0047</t>
+  </si>
+  <si>
+    <t>0.0844,0.3395,0.7034,0.0144</t>
+  </si>
+  <si>
+    <t>0.0750,0.4403,0.6751,0.0226</t>
+  </si>
+  <si>
+    <t>0.0552,0.3760,0.7694,0.0108</t>
+  </si>
+  <si>
+    <t>0.3166,0.5200,0.1178,0.1486</t>
+  </si>
+  <si>
+    <t>0.4613,0.2081,0.3325,0.0159</t>
+  </si>
+  <si>
+    <t>0.4977,0.1256,0.3986,0.0183</t>
+  </si>
+  <si>
+    <t>0.5250,0.2129,0.2011,0.0405</t>
+  </si>
+  <si>
+    <t>0.0134,0.0515,0.0034,0.9835</t>
+  </si>
+  <si>
+    <t>0.0007,0.0051,0.0028,0.9982</t>
+  </si>
+  <si>
+    <t>0.0013,0.0542,0.0014,0.9957</t>
+  </si>
+  <si>
+    <t>0.0065,0.0213,0.0055,0.9914</t>
+  </si>
+  <si>
+    <t>0.0077,0.8737,0.7788,0.0091</t>
+  </si>
+  <si>
+    <t>0.9043,0.1142,0.0030,0.0131</t>
+  </si>
+  <si>
+    <t>0.1574,0.8697,0.0063,0.0066</t>
+  </si>
+  <si>
+    <t>0.9087,0.0982,0.0088,0.0146</t>
+  </si>
+  <si>
+    <t>0.2252,0.8088,0.0142,0.0136</t>
+  </si>
+  <si>
+    <t>0.8043,0.2206,0.0183,0.0120</t>
+  </si>
+  <si>
+    <t>0.4897,0.3072,0.1926,0.0898</t>
+  </si>
+  <si>
+    <t>0.9529,0.0449,0.0034,0.0099</t>
+  </si>
+  <si>
+    <t>0.0123,0.1014,0.9324,0.0872</t>
+  </si>
+  <si>
+    <t>0.6921,0.1313,0.1154,0.0853</t>
+  </si>
+  <si>
+    <t>0.6159,0.2749,0.0171,0.1129</t>
+  </si>
+  <si>
+    <t>0.0374,0.9444,0.0077,0.0114</t>
+  </si>
+  <si>
+    <t>0.5945,0.3928,0.0741,0.0281</t>
+  </si>
+  <si>
+    <t>0.1704,0.8486,0.0209,0.0066</t>
+  </si>
+  <si>
+    <t>0.0539,0.9101,0.0349,0.0159</t>
+  </si>
+  <si>
+    <t>0.2750,0.6453,0.1087,0.0115</t>
+  </si>
+  <si>
+    <t>0.1922,0.7874,0.0455,0.0164</t>
+  </si>
+  <si>
+    <t>0.9036,0.0924,0.0063,0.0226</t>
+  </si>
+  <si>
+    <t>0.9419,0.0360,0.0038,0.0224</t>
+  </si>
+  <si>
+    <t>0.9390,0.0635,0.0060,0.0099</t>
+  </si>
+  <si>
+    <t>0.9605,0.0280,0.0038,0.0140</t>
+  </si>
+  <si>
+    <t>0.9562,0.0266,0.0035,0.0179</t>
+  </si>
+  <si>
+    <t>0.9285,0.1091,0.0033,0.0043</t>
+  </si>
+  <si>
+    <t>0.9516,0.0431,0.0027,0.0149</t>
+  </si>
+  <si>
+    <t>0.9572,0.0580,0.0027,0.0065</t>
+  </si>
+  <si>
+    <t>0.0538,0.9505,0.0054,0.0017</t>
+  </si>
+  <si>
+    <t>0.3708,0.7557,0.0060,0.0016</t>
+  </si>
+  <si>
+    <t>0.0768,0.9346,0.0061,0.0023</t>
+  </si>
+  <si>
+    <t>0.1523,0.8397,0.0442,0.0090</t>
+  </si>
+  <si>
+    <t>0.7541,0.3697,0.0069,0.0042</t>
+  </si>
+  <si>
+    <t>0.3489,0.7585,0.0084,0.0037</t>
+  </si>
+  <si>
+    <t>0.7300,0.4279,0.0039,0.0027</t>
+  </si>
+  <si>
+    <t>0.2999,0.7674,0.0071,0.0039</t>
+  </si>
+  <si>
+    <t>0.0039,0.1855,0.9882,0.0017</t>
+  </si>
+  <si>
+    <t>0.3337,0.7433,0.0114,0.0096</t>
+  </si>
+  <si>
+    <t>0.0489,0.0094,0.9521,0.0098</t>
+  </si>
+  <si>
+    <t>0.0517,0.2968,0.8526,0.0445</t>
+  </si>
+  <si>
+    <t>0.1201,0.0384,0.8807,0.0083</t>
+  </si>
+  <si>
+    <t>0.0815,0.5377,0.6595,0.0217</t>
+  </si>
+  <si>
+    <t>0.3096,0.0627,0.6734,0.0510</t>
+  </si>
+  <si>
+    <t>0.0811,0.0149,0.9331,0.0074</t>
+  </si>
+  <si>
+    <t>0.0465,0.0280,0.9406,0.0162</t>
+  </si>
+  <si>
+    <t>0.2369,0.3423,0.4237,0.0278</t>
+  </si>
+  <si>
+    <t>0.2277,0.1912,0.6118,0.0199</t>
+  </si>
+  <si>
+    <t>0.3245,0.5122,0.0938,0.0144</t>
+  </si>
+  <si>
+    <t>0.0851,0.8390,0.0852,0.0079</t>
+  </si>
+  <si>
+    <t>0.0417,0.8246,0.1819,0.0053</t>
+  </si>
+  <si>
+    <t>0.4841,0.2665,0.2384,0.0311</t>
+  </si>
+  <si>
+    <t>0.2357,0.4028,0.2143,0.3947</t>
+  </si>
+  <si>
+    <t>0.2091,0.6146,0.1780,0.0583</t>
+  </si>
+  <si>
+    <t>0.1783,0.8819,0.0060,0.0015</t>
+  </si>
+  <si>
+    <t>0.2322,0.8383,0.0053,0.0022</t>
+  </si>
+  <si>
+    <t>0.1714,0.8644,0.0091,0.0030</t>
+  </si>
+  <si>
+    <t>0.4352,0.6867,0.0046,0.0052</t>
+  </si>
+  <si>
+    <t>0.6862,0.4828,0.0026,0.0036</t>
+  </si>
+  <si>
+    <t>0.1158,0.8115,0.0840,0.0207</t>
+  </si>
+  <si>
+    <t>0.5766,0.1996,0.1521,0.0218</t>
+  </si>
+  <si>
+    <t>0.5491,0.1733,0.2276,0.0762</t>
+  </si>
+  <si>
+    <t>0.4455,0.2312,0.3058,0.1071</t>
+  </si>
+  <si>
+    <t>0.3152,0.5146,0.1620,0.0489</t>
+  </si>
+  <si>
+    <t>0.0594,0.1489,0.8730,0.0964</t>
+  </si>
+  <si>
+    <t>0.2668,0.2219,0.5502,0.1045</t>
+  </si>
+  <si>
+    <t>0.3146,0.0995,0.4212,0.2113</t>
+  </si>
+  <si>
+    <t>0.2080,0.2393,0.6252,0.0667</t>
+  </si>
+  <si>
+    <t>0.0882,0.4903,0.5371,0.0208</t>
+  </si>
+  <si>
+    <t>0.9429,0.0749,0.0025,0.0080</t>
+  </si>
+  <si>
+    <t>0.8840,0.1727,0.0045,0.0086</t>
+  </si>
+  <si>
+    <t>0.8283,0.2669,0.0048,0.0056</t>
+  </si>
+  <si>
+    <t>0.9438,0.1039,0.0017,0.0020</t>
+  </si>
+  <si>
+    <t>0.8333,0.2438,0.0066,0.0032</t>
+  </si>
+  <si>
+    <t>0.9425,0.1067,0.0024,0.0021</t>
+  </si>
+  <si>
+    <t>0.9076,0.1246,0.0039,0.0135</t>
+  </si>
+  <si>
+    <t>0.9564,0.0650,0.0033,0.0040</t>
+  </si>
+  <si>
+    <t>0.1484,0.5086,0.3927,0.0152</t>
+  </si>
+  <si>
+    <t>0.2107,0.3898,0.4206,0.0195</t>
+  </si>
+  <si>
+    <t>0.2945,0.5803,0.0651,0.1429</t>
+  </si>
+  <si>
+    <t>0.0457,0.0164,0.9636,0.0028</t>
+  </si>
+  <si>
+    <t>0.0415,0.0173,0.8977,0.0729</t>
+  </si>
+  <si>
+    <t>0.1151,0.1031,0.8236,0.0235</t>
+  </si>
+  <si>
+    <t>0.0162,0.0167,0.9807,0.0109</t>
+  </si>
+  <si>
+    <t>0.1364,0.3781,0.5336,0.0946</t>
+  </si>
+  <si>
+    <t>0.0412,0.0314,0.9440,0.0332</t>
+  </si>
+  <si>
+    <t>0.1032,0.1450,0.7405,0.1025</t>
+  </si>
+  <si>
+    <t>0.1208,0.5414,0.3899,0.1546</t>
+  </si>
+  <si>
+    <t>0.5552,0.1099,0.3114,0.0438</t>
+  </si>
+  <si>
+    <t>0.6419,0.0256,0.3430,0.0358</t>
+  </si>
+  <si>
+    <t>0.7103,0.0675,0.1299,0.0513</t>
+  </si>
+  <si>
+    <t>0.8349,0.2240,0.0066,0.0116</t>
+  </si>
+  <si>
+    <t>0.9468,0.0852,0.0027,0.0038</t>
+  </si>
+  <si>
+    <t>0.9657,0.0397,0.0041,0.0048</t>
+  </si>
+  <si>
+    <t>0.9271,0.1018,0.0035,0.0080</t>
+  </si>
+  <si>
+    <t>0.9279,0.0840,0.0037,0.0146</t>
+  </si>
+  <si>
+    <t>0.7965,0.3241,0.0046,0.0036</t>
+  </si>
+  <si>
+    <t>0.9076,0.1470,0.0028,0.0050</t>
+  </si>
+  <si>
+    <t>0.9493,0.0715,0.0023,0.0062</t>
+  </si>
+  <si>
+    <t>0.1066,0.0633,0.8709,0.0068</t>
+  </si>
+  <si>
+    <t>0.0103,0.0884,0.9787,0.0029</t>
+  </si>
+  <si>
+    <t>0.0600,0.3757,0.8028,0.0234</t>
+  </si>
+  <si>
+    <t>0.3791,0.0522,0.6279,0.0074</t>
+  </si>
+  <si>
+    <t>0.0469,0.0182,0.8973,0.0600</t>
+  </si>
+  <si>
+    <t>0.2141,0.3963,0.4320,0.1324</t>
+  </si>
+  <si>
+    <t>0.1828,0.0883,0.7863,0.0224</t>
+  </si>
+  <si>
+    <t>0.1223,0.0686,0.8454,0.0385</t>
+  </si>
+  <si>
+    <t>0.4134,0.1050,0.0273,0.5147</t>
+  </si>
+  <si>
+    <t>0.0034,0.1028,0.0053,0.9872</t>
+  </si>
+  <si>
+    <t>0.0120,0.0535,0.0055,0.9843</t>
+  </si>
+  <si>
+    <t>0.0013,0.0187,0.0011,0.9975</t>
+  </si>
+  <si>
+    <t>0.0023,0.0143,0.0016,0.9968</t>
+  </si>
+  <si>
+    <t>0.2513,0.3929,0.0912,0.4463</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>262</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2133,7 @@
         <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2144,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2158,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2172,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2189,7 @@
         <v>262</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2273,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2385,7 @@
         <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2413,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,10 +2424,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>262</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2455,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>262</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>262</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>262</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2931,7 @@
         <v>262</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2942,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2973,7 @@
         <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2987,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,7 +3127,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3138,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3166,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3558,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3589,7 @@
         <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3701,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3715,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3717,10 +3726,10 @@
         <v>259</v>
       </c>
       <c r="C128" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3880,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3894,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3908,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3922,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4037,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4065,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4135,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4137,10 +4146,10 @@
         <v>259</v>
       </c>
       <c r="C158" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4163,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4191,7 @@
         <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>262</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>262</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4373,7 @@
         <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,10 +4412,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>262</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,10 +4482,10 @@
         <v>259</v>
       </c>
       <c r="C182" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4510,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4639,7 @@
         <v>262</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4650,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4709,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4723,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4737,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,10 +4748,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4753,10 +4762,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4793,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4809,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4823,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4860,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4874,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4888,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5028,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5047,10 +5056,10 @@
         <v>259</v>
       </c>
       <c r="C223" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5168,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5336,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5364,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5420,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,7 +5451,7 @@
         <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5518,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
